--- a/analysis/OSD_Statistical_Analyses.xlsx
+++ b/analysis/OSD_Statistical_Analyses.xlsx
@@ -17,11 +17,12 @@
     <sheet name="Trends" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Models" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Advancement" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Cohorts" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Projections" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Finance" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Capacity" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Forecast_accuracy" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Welch_sensitivity" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Cohorts" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Projections" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Finance" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Capacity" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Forecast_accuracy" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="434">
   <si>
     <t xml:space="preserve">OSD Elementary Closure Community Analysis: statistical workbook</t>
   </si>
@@ -68,6 +69,9 @@
     <t xml:space="preserve">Period comparisons of advancement ratios: Welch two-sample t-tests, 2010-2019 vs. 2022-2026 (2020 and 2021 COVID transitions excluded).</t>
   </si>
   <si>
+    <t xml:space="preserve">Dependence check: because each year can depend on the year before, the Welch tests were checked for serial correlation (Welch_sensitivity tab). Advancement ratios are year-over-year growth rates and show little serial correlation (average lag-1 autocorrelation -0.20 for K-5, -0.01 for K-12); an effective-sample-size adjustment leaves every K-5 result unchanged, and a permutation test agrees with Welch for every K-5 transition. Welch is therefore appropriate, with no correction applied.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Model comparison: AIC = n ln(RSS/n) + 2k, k = number of fitted coefficients.</t>
   </si>
   <si>
@@ -89,7 +93,7 @@
     <t xml:space="preserve">Reported figures compared with reproduced values</t>
   </si>
   <si>
-    <t xml:space="preserve">MATCH = reproduced exactly at the report's precision. ROUNDING = differs only by rounding. Checked against the final report of Oct. 12, 2026.</t>
+    <t xml:space="preserve">MATCH = reproduced exactly at the report's precision. ROUNDING = differs only by rounding. Checked against the final report as updated Oct. 13, 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Report location</t>
@@ -203,6 +207,36 @@
     <t xml:space="preserve">2021 K-to-1 ratio 1.036 (K-5)</t>
   </si>
   <si>
+    <t xml:space="preserve">Appendix A10, methods note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependence check for Welch tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average lag-1 autocorrelation -0.20 (K-5), -0.01 (K-12); every K-5 result unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.20 and -0.01; K-5 effective-n p identical to Welch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See Welch_sensitivity tab; permutation test agrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrollment, "Families join at every grade"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K to 1 ratio before and after COVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.053 before, 1.069 after; no significant change; most slightly higher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identical (4 of 5 K-5 transitions higher)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wording changed Oct. 13 from "the same as before COVID"</t>
+  </si>
+  <si>
     <t xml:space="preserve">Table A11.1</t>
   </si>
   <si>
@@ -789,6 +823,69 @@
   </si>
   <si>
     <t xml:space="preserve">11 to 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependence check for the Welch tests (Appendix A10 methods note)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values from reproduce.py (permutation seeds 20261013 and 20261014). Question: does year-to-year dependence make the Welch p-values in Tables A10.1 and A10.2 unreliable?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why check: enrollment in one year depends on the year before, which is why full-period headcount trends use Newey-West standard errors. Welch corrects for unequal variances, not for dependence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lag-1 autocorrelation: correlation of each ratio with the next year's ratio for the same transition, measured around each period's own mean (pairs within a period only).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective-n Welch p: Welch recomputed with n_eff = n(1 - rho)/(1 + rho) when rho &gt; 0; when rho &lt;= 0 it equals the Welch p (negative autocorrelation is not used to enlarge n).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permutation p: share of 20,000 random relabelings of the 15 years whose before-after difference is at least as large as observed. It makes no normality or equal-variance assumption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newey-West is not used here: with 15 observations it tends to understate standard errors, and with near-zero autocorrelation it offers no benefit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-5, 11 neighborhood schools (Table A10.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lag-1 autocorrelation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welch p (reported)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective-n Welch p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permutation p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-12, all programs including ORLA (Table A10.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advancement ratios are growth rates, so they carry little of the year-to-year persistence seen in headcounts; most autocorrelations are near zero or negative, which if anything makes Welch slightly conservative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every K-5 result is unchanged by the effective-n adjustment, and the permutation test agrees with Welch. No K-5 transition changed significantly after COVID, and four of five are slightly higher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One exception, which the report does not rely on: 11 to 12 in K-12 has strong positive autocorrelation (+0.62); its Welch p of 0.01 rises to about 0.34 after adjustment. With 17 tests in the two tables, one p near 0.01 is about what chance alone would produce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In K-12, the permutation test gives a lower p for 5 to 6 (0.03, against Welch 0.08), pointing the same way as the report: classes grow at 6th grade since COVID. The report states that growth as a measured figure and does not rest on either test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With 10 and 5 years per period these tests detect only large changes, so a non-significant result means no detectable change, not proof of equality.</t>
   </si>
   <si>
     <t xml:space="preserve">Kindergarten classes tracked to 5th grade (Table A11.1)</t>
@@ -1245,7 +1342,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1253,10 +1350,11 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="\+0.0%;\-0.0%"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
-    <numFmt numFmtId="173" formatCode="0%"/>
-    <numFmt numFmtId="174" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="\+0.00;\-0.00"/>
+    <numFmt numFmtId="172" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0"/>
+    <numFmt numFmtId="174" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1371,7 +1469,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1444,7 +1542,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1452,15 +1558,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1468,15 +1570,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1488,7 +1594,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1744,7 +1850,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -1811,40 +1917,45 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1863,258 +1974,542 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <f aca="false">Data_K5!B5</f>
-        <v>570</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <f aca="false">Data_K5!G10</f>
-        <v>650</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <f aca="false">C5/B5-1</f>
-        <v>0.140350877192982</v>
+      <c r="A5" s="5" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <f aca="false">Data_K5!B6</f>
-        <v>581</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <f aca="false">Data_K5!G11</f>
-        <v>680</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <f aca="false">C6/B6-1</f>
-        <v>0.17039586919105</v>
+      <c r="A6" s="5" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <f aca="false">Data_K5!B7</f>
-        <v>566</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <f aca="false">Data_K5!G12</f>
-        <v>677</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <f aca="false">C7/B7-1</f>
-        <v>0.196113074204947</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <f aca="false">Data_K5!B8</f>
-        <v>593</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <f aca="false">Data_K5!G13</f>
-        <v>696</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <f aca="false">C8/B8-1</f>
-        <v>0.173693086003373</v>
+      <c r="A7" s="5" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <f aca="false">Data_K5!B9</f>
-        <v>586</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <f aca="false">Data_K5!G14</f>
-        <v>678</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <f aca="false">C9/B9-1</f>
-        <v>0.156996587030717</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <f aca="false">Data_K5!B10</f>
-        <v>623</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <f aca="false">Data_K5!G15</f>
-        <v>728</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">C10/B10-1</f>
-        <v>0.168539325842697</v>
+      <c r="A9" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <f aca="false">Data_K5!B11</f>
-        <v>558</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <f aca="false">Data_K5!G16</f>
-        <v>650</v>
+        <v>245</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>1.0531106532649</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>1.06857652093159</v>
       </c>
       <c r="D11" s="17" t="n">
-        <f aca="false">C11/B11-1</f>
-        <v>0.164874551971326</v>
+        <v>-0.497763224145217</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.414349850055125</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.414349850055125</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.43075</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <f aca="false">Data_K5!B12</f>
-        <v>582</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <f aca="false">Data_K5!G17</f>
-        <v>569</v>
+        <v>246</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>1.02631116249691</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>1.02404895125028</v>
       </c>
       <c r="D12" s="17" t="n">
-        <f aca="false">C12/B12-1</f>
-        <v>-0.0223367697594502</v>
+        <v>-0.00404213735099766</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.856451162026728</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.856451162026728</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.8832</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="7" t="n">
-        <f aca="false">Data_K5!B13</f>
-        <v>626</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <f aca="false">Data_K5!G18</f>
-        <v>711</v>
+        <v>247</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>1.01057636019575</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>1.03567763936923</v>
       </c>
       <c r="D13" s="17" t="n">
-        <f aca="false">C13/B13-1</f>
-        <v>0.135782747603834</v>
+        <v>-0.0215272677446195</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0572938944800338</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.0572938944800338</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.05765</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <f aca="false">Data_K5!B14</f>
-        <v>637</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <f aca="false">Data_K5!G19</f>
-        <v>604</v>
+        <v>248</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>1.02394347429259</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>1.03533536961824</v>
       </c>
       <c r="D14" s="17" t="n">
-        <f aca="false">C14/B14-1</f>
-        <v>-0.0518053375196232</v>
+        <v>-0.172303803195449</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.453242811324108</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0.453242811324108</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0.36735</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <f aca="false">Data_K5!B15</f>
-        <v>684</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <f aca="false">Data_K5!G20</f>
-        <v>656</v>
+        <v>249</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>1.02404180077317</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>1.02641221237803</v>
       </c>
       <c r="D15" s="17" t="n">
-        <f aca="false">C15/B15-1</f>
-        <v>-0.0409356725146199</v>
+        <v>-0.28678770046716</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.908970988958654</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.908970988958654</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.88435</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <f aca="false">Data_K5!B16</f>
-        <v>525</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <f aca="false">Data_K5!G21</f>
-        <v>625</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <f aca="false">C16/B16-1</f>
-        <v>0.19047619047619</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="7" t="n">
-        <f aca="false">Data_K5!B17</f>
-        <v>534</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <f aca="false">Data_K5!G22</f>
-        <v>631</v>
-      </c>
-      <c r="D17" s="17" t="n">
-        <f aca="false">C17/B17-1</f>
-        <v>0.181647940074906</v>
+      <c r="A16" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">AVERAGE(D11:D15)</f>
+        <v>-0.196484826580689</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>1.05886644447588</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>1.07103676617793</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>-0.370836652951018</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.514873186810778</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>0.514873186810778</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.4994</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>1.02664099663183</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>1.02585752169022</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>-0.0352853506267944</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.937506839266454</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0.937506839266454</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0.95215</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>1.01126242083432</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>1.02687310590056</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>-0.0591795852937183</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.105068694906958</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0.105068694906958</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0.0989</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>1.02246480850137</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>1.02122780168511</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0.22751682466983</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.884108525462452</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0.909786806595424</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.88595</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1.02344773454959</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>1.01778633406654</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>-0.221211494333062</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.594815125199203</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0.594815125199203</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0.5915</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>0.995198569405975</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>1.02197300381397</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>-0.302173996618462</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0777739636087424</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0.0777739636087424</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.02635</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>1.02864703024254</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1.02785740536933</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>-0.196504331640819</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.96245766029567</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0.96245766029567</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0.95855</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>1.01305845858892</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>1.0086979134887</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>0.208147571404108</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.562156099255427</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0.645232091063966</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0.58585</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>1.23255474749898</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>1.2072808674242</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>-0.0262415356500626</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.137218947358736</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0.137218947358736</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0.14135</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>0.998461669922631</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>1.00636114097535</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>-0.263403779299008</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.492826784886179</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0.492826784886179</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.36905</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>0.94738403864498</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>0.957957911678187</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0.268766455767104</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.37704015522335</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0.511422525196177</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0.4742</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>0.986092682477731</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>0.943697287639025</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>0.623997042493866</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0053179733572569</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0.33694656986938</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0.0244</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <f aca="false">AVERAGE(D20:D31)</f>
+        <v>-0.012200736006503</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2129,6 +2524,276 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <f aca="false">Data_K5!B5</f>
+        <v>570</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <f aca="false">Data_K5!G10</f>
+        <v>650</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <f aca="false">C5/B5-1</f>
+        <v>0.140350877192982</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <f aca="false">Data_K5!B6</f>
+        <v>581</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <f aca="false">Data_K5!G11</f>
+        <v>680</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <f aca="false">C6/B6-1</f>
+        <v>0.17039586919105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <f aca="false">Data_K5!B7</f>
+        <v>566</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <f aca="false">Data_K5!G12</f>
+        <v>677</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <f aca="false">C7/B7-1</f>
+        <v>0.196113074204947</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">Data_K5!B8</f>
+        <v>593</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <f aca="false">Data_K5!G13</f>
+        <v>696</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">C8/B8-1</f>
+        <v>0.173693086003373</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <f aca="false">Data_K5!B9</f>
+        <v>586</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <f aca="false">Data_K5!G14</f>
+        <v>678</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <f aca="false">C9/B9-1</f>
+        <v>0.156996587030717</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <f aca="false">Data_K5!B10</f>
+        <v>623</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <f aca="false">Data_K5!G15</f>
+        <v>728</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <f aca="false">C10/B10-1</f>
+        <v>0.168539325842697</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <f aca="false">Data_K5!B11</f>
+        <v>558</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <f aca="false">Data_K5!G16</f>
+        <v>650</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">C11/B11-1</f>
+        <v>0.164874551971326</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">Data_K5!B12</f>
+        <v>582</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <f aca="false">Data_K5!G17</f>
+        <v>569</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <f aca="false">C12/B12-1</f>
+        <v>-0.0223367697594502</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <f aca="false">Data_K5!B13</f>
+        <v>626</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <f aca="false">Data_K5!G18</f>
+        <v>711</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <f aca="false">C13/B13-1</f>
+        <v>0.135782747603834</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <f aca="false">Data_K5!B14</f>
+        <v>637</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <f aca="false">Data_K5!G19</f>
+        <v>604</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <f aca="false">C14/B14-1</f>
+        <v>-0.0518053375196232</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <f aca="false">Data_K5!B15</f>
+        <v>684</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <f aca="false">Data_K5!G20</f>
+        <v>656</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <f aca="false">C15/B15-1</f>
+        <v>-0.0409356725146199</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <f aca="false">Data_K5!B16</f>
+        <v>525</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <f aca="false">Data_K5!G21</f>
+        <v>625</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <f aca="false">C16/B16-1</f>
+        <v>0.19047619047619</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <f aca="false">Data_K5!B17</f>
+        <v>534</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <f aca="false">Data_K5!G22</f>
+        <v>631</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <f aca="false">C17/B17-1</f>
+        <v>0.181647940074906</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2146,45 +2811,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3068.72171505131</v>
@@ -2207,7 +2872,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>3032.27862153934</v>
@@ -2230,7 +2895,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>2999.79350797927</v>
@@ -2253,32 +2918,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>3523.00182036714</v>
@@ -2298,7 +2963,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>3448.70318894931</v>
@@ -2318,7 +2983,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>3407.0875073086</v>
@@ -2338,7 +3003,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>3399.27149735955</v>
@@ -2358,7 +3023,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>3397.56545717758</v>
@@ -2378,7 +3043,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>3397.56545717758</v>
@@ -2398,7 +3063,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>3397.56545717758</v>
@@ -2418,7 +3083,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>3397.56545717758</v>
@@ -2438,45 +3103,45 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2528,7 +3193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2545,229 +3210,229 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B5" s="18" t="n">
+        <v>315</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <v>14800</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>741</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>1756</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B8" s="19" t="n">
+        <v>321</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <v>3.14</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="20" t="n">
+        <v>323</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>392953</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B10" s="20" t="n">
+        <v>324</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>86744</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B12" s="19" t="n">
+        <v>328</v>
+      </c>
+      <c r="B12" s="21" t="n">
         <v>195.67</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="19" t="n">
+        <v>330</v>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>190.15</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="21" t="n">
+        <v>331</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>0.83</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B15" s="19" t="n">
+        <v>333</v>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>8.41</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="23" t="n">
         <v>0.02</v>
       </c>
       <c r="B19" s="7" t="n">
         <f aca="false">ROUND($B$6*A19,0)</f>
         <v>15</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="24" t="n">
         <f aca="false">B19*$B$5</f>
         <v>222000</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="25" t="n">
         <f aca="false">C19/3100000</f>
         <v>0.0716129032258065</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">ROUND($B$6*A20,0)</f>
         <v>37</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="24" t="n">
         <f aca="false">B20*$B$5</f>
         <v>547600</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="25" t="n">
         <f aca="false">C20/3100000</f>
         <v>0.176645161290323</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">ROUND($B$6*A21,0)</f>
         <v>74</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="24" t="n">
         <f aca="false">B21*$B$5</f>
         <v>1095200</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">C21/3100000</f>
         <v>0.353290322580645</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">ROUND(0.05*$B$6,0)</f>
@@ -2780,7 +3445,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">ROUND(0.05*$B$6,0)+ROUND(0.01*$B$7,0)</f>
@@ -2793,7 +3458,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="B27" s="7" t="n">
         <f aca="false">ROUND(0.05*$B$6,0)+ROUND(0.02*$B$7,0)</f>
@@ -2806,7 +3471,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="B28" s="7" t="n">
         <f aca="false">ROUND(0.05*($B$6+$B$7),0)</f>
@@ -2819,26 +3484,26 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="B32" s="15" t="n">
         <f aca="false">$B$8</f>
@@ -2851,7 +3516,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>-0.1</v>
@@ -2860,12 +3525,12 @@
         <v>-0.21</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="B34" s="15" t="n">
         <f aca="false">-ROUND($B$11*0.5/8,1)*$B$10/1000000</f>
@@ -2876,12 +3541,12 @@
         <v>-0.3729992</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>0</v>
@@ -2892,7 +3557,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="B36" s="15" t="n">
         <f aca="false">-C26</f>
@@ -2905,93 +3570,93 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B37" s="24" t="n">
+        <v>357</v>
+      </c>
+      <c r="B37" s="26" t="n">
         <f aca="false">SUM(B32:B36)</f>
         <v>1.9917912</v>
       </c>
-      <c r="C37" s="24" t="n">
+      <c r="C37" s="26" t="n">
         <f aca="false">SUM(C32:C36)</f>
         <v>1.3314008</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="B38" s="23" t="n">
+        <v>358</v>
+      </c>
+      <c r="B38" s="25" t="n">
         <f aca="false">1-B37/$B$8</f>
         <v>0.365671592356688</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="25" t="n">
         <f aca="false">1-C37/$B$8</f>
         <v>0.575987006369427</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B41" s="22" t="n">
+        <v>360</v>
+      </c>
+      <c r="B41" s="24" t="n">
         <f aca="false">0.3*$B$9</f>
         <v>117885.9</v>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="24" t="n">
         <f aca="false">0.5*$B$9</f>
         <v>196476.5</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B42" s="22" t="n">
+        <v>361</v>
+      </c>
+      <c r="B42" s="24" t="n">
         <f aca="false">0.25*$B$10</f>
         <v>21686</v>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="24" t="n">
         <f aca="false">0.5*$B$10</f>
         <v>43372</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B43" s="20" t="n">
+        <v>362</v>
+      </c>
+      <c r="B43" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="22" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B44" s="25" t="n">
+        <v>363</v>
+      </c>
+      <c r="B44" s="27" t="n">
         <f aca="false">SUM(B41:B43)</f>
         <v>149571.9</v>
       </c>
-      <c r="C44" s="25" t="n">
+      <c r="C44" s="27" t="n">
         <f aca="false">SUM(C41:C43)</f>
         <v>259848.5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">$B$12*$B$14/12</f>
@@ -3000,7 +3665,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="B48" s="10" t="n">
         <f aca="false">B47/$B$12</f>
@@ -3009,7 +3674,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="B49" s="10" t="n">
         <f aca="false">B47/$B$13</f>
@@ -3018,16 +3683,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B50" s="22" t="n">
+        <v>368</v>
+      </c>
+      <c r="B50" s="24" t="n">
         <f aca="false">206000*313/(313+256)</f>
         <v>113318.101933216</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B51" s="10" t="n">
         <f aca="false">(0.44+0.44+0.527)/3</f>
@@ -3044,7 +3709,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="B52" s="10" t="n">
         <f aca="false">(0.44+0.44+0.517)/3</f>
@@ -3061,7 +3726,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="B53" s="15" t="n">
         <f aca="false">744/642</f>
@@ -3070,7 +3735,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="B54" s="15" t="n">
         <f aca="false">513/576</f>
@@ -3079,7 +3744,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="B55" s="7" t="n">
         <f aca="false">ROUND(576*1.08,0)-513</f>
@@ -3092,7 +3757,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="B56" s="7" t="n">
         <f aca="false">ROUND(459*(1.08-0.96),0)</f>
@@ -3105,94 +3770,94 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B57" s="26" t="n">
+        <v>375</v>
+      </c>
+      <c r="B57" s="28" t="n">
         <f aca="false">50/(1.08-0.96)</f>
         <v>416.666666666666</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="B61" s="19" t="n">
+        <v>381</v>
+      </c>
+      <c r="B61" s="21" t="n">
         <v>0.41</v>
       </c>
-      <c r="C61" s="19" t="n">
+      <c r="C61" s="21" t="n">
         <v>0.37</v>
       </c>
-      <c r="D61" s="19" t="n">
+      <c r="D61" s="21" t="n">
         <v>0.36</v>
       </c>
-      <c r="E61" s="19" t="n">
+      <c r="E61" s="21" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B62" s="19" t="n">
+        <v>382</v>
+      </c>
+      <c r="B62" s="21" t="n">
         <v>195.67</v>
       </c>
-      <c r="C62" s="19" t="n">
+      <c r="C62" s="21" t="n">
         <v>202.93</v>
       </c>
-      <c r="D62" s="19" t="n">
+      <c r="D62" s="21" t="n">
         <v>207.89</v>
       </c>
-      <c r="E62" s="19" t="n">
+      <c r="E62" s="21" t="n">
         <v>212.52</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B63" s="27" t="n">
+        <v>383</v>
+      </c>
+      <c r="B63" s="29" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B64" s="28" t="n">
+        <v>384</v>
+      </c>
+      <c r="B64" s="30" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B65" s="29" t="n">
+        <v>385</v>
+      </c>
+      <c r="B65" s="31" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="B66" s="16" t="n">
         <f aca="false">0.155+0.305+0.08</f>
@@ -3201,7 +3866,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="B67" s="13" t="n">
         <f aca="false">0.05*$B$6+0.015*$B$7</f>
@@ -3210,36 +3875,36 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B70" s="10" t="n">
         <f aca="false">H70/B$62</f>
@@ -3276,7 +3941,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="B71" s="10" t="n">
         <f aca="false">H71/B$62</f>
@@ -3313,7 +3978,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="B72" s="10" t="n">
         <f aca="false">H72/B$62</f>
@@ -3350,7 +4015,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="B73" s="10" t="n">
         <f aca="false">H73/B$62</f>
@@ -3387,7 +4052,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="B74" s="10" t="n">
         <f aca="false">H74/B$62</f>
@@ -3424,7 +4089,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="B75" s="10" t="n">
         <f aca="false">H75/B$62</f>
@@ -3461,7 +4126,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="B76" s="10" t="n">
         <f aca="false">H76/B$62</f>
@@ -3498,7 +4163,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="B77" s="10" t="n">
         <f aca="false">H77/B$62</f>
@@ -3535,7 +4200,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="B78" s="10" t="n">
         <f aca="false">H78/B$62</f>
@@ -3572,18 +4237,18 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B80" s="26" t="n">
+        <v>399</v>
+      </c>
+      <c r="B80" s="28" t="n">
         <f aca="false">($B$8-$B$66)*1000000/$B$5</f>
         <v>175.675675675676</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B81" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="B81" s="28" t="n">
         <f aca="false">($B$8-$B$66-B61)*1000000/$B$5</f>
         <v>147.972972972973</v>
       </c>
@@ -3599,7 +4264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3617,33 +4282,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B4" s="28" t="n">
+        <v>403</v>
+      </c>
+      <c r="B4" s="30" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B5" s="28" t="n">
+        <v>404</v>
+      </c>
+      <c r="B5" s="30" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">(4*B4+2*B5)/6</f>
@@ -3652,7 +4317,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>25</v>
@@ -3660,7 +4325,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>10</v>
@@ -3668,50 +4333,50 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="28" t="n">
+        <v>408</v>
+      </c>
+      <c r="B9" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="30" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>509</v>
@@ -3726,30 +4391,30 @@
         <f aca="false">(C12-D12)*$B$7+D12*$B$8</f>
         <v>570</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">B12/E12</f>
         <v>0.892982456140351</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="28" t="n">
         <f aca="false">(C12-D12)*$B$6+D12*$B$8</f>
         <v>496.666666666667</v>
       </c>
-      <c r="H12" s="23" t="n">
+      <c r="H12" s="25" t="n">
         <f aca="false">B12/G12</f>
         <v>1.0248322147651</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="25" t="n">
         <f aca="false">B12/((C12-D12)*$B$9+D12*$B$8)</f>
         <v>0.928832116788321</v>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="25" t="n">
         <f aca="false">B12/((C12-D12)*$C$9+D12*$B$8)</f>
         <v>1.05601659751037</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>429</v>
@@ -3764,30 +4429,30 @@
         <f aca="false">(C13-D13)*$B$7+D13*$B$8</f>
         <v>485</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">B13/E13</f>
         <v>0.884536082474227</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">(C13-D13)*$B$6+D13*$B$8</f>
         <v>421.666666666667</v>
       </c>
-      <c r="H13" s="23" t="n">
+      <c r="H13" s="25" t="n">
         <f aca="false">B13/G13</f>
         <v>1.01739130434783</v>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="25" t="n">
         <f aca="false">B13/((C13-D13)*$B$9+D13*$B$8)</f>
         <v>0.920600858369099</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="25" t="n">
         <f aca="false">B13/((C13-D13)*$C$9+D13*$B$8)</f>
         <v>1.04889975550122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>498</v>
@@ -3802,30 +4467,30 @@
         <f aca="false">(C14-D14)*$B$7+D14*$B$8</f>
         <v>595</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="25" t="n">
         <f aca="false">B14/E14</f>
         <v>0.836974789915966</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="28" t="n">
         <f aca="false">(C14-D14)*$B$6+D14*$B$8</f>
         <v>518.333333333333</v>
       </c>
-      <c r="H14" s="23" t="n">
+      <c r="H14" s="25" t="n">
         <f aca="false">B14/G14</f>
         <v>0.960771704180064</v>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="25" t="n">
         <f aca="false">B14/((C14-D14)*$B$9+D14*$B$8)</f>
         <v>0.870629370629371</v>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="J14" s="25" t="n">
         <f aca="false">B14/((C14-D14)*$C$9+D14*$B$8)</f>
         <v>0.990059642147117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>478</v>
@@ -3840,30 +4505,30 @@
         <f aca="false">(C15-D15)*$B$7+D15*$B$8</f>
         <v>570</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">B15/E15</f>
         <v>0.83859649122807</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="28" t="n">
         <f aca="false">(C15-D15)*$B$6+D15*$B$8</f>
         <v>496.666666666667</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="H15" s="25" t="n">
         <f aca="false">B15/G15</f>
         <v>0.96241610738255</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="25" t="n">
         <f aca="false">B15/((C15-D15)*$B$9+D15*$B$8)</f>
         <v>0.872262773722628</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="25" t="n">
         <f aca="false">B15/((C15-D15)*$C$9+D15*$B$8)</f>
         <v>0.991701244813278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>494</v>
@@ -3878,35 +4543,35 @@
         <f aca="false">(C16-D16)*$B$7+D16*$B$8</f>
         <v>670</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">B16/E16</f>
         <v>0.737313432835821</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="28" t="n">
         <f aca="false">(C16-D16)*$B$6+D16*$B$8</f>
         <v>583.333333333333</v>
       </c>
-      <c r="H16" s="23" t="n">
+      <c r="H16" s="25" t="n">
         <f aca="false">B16/G16</f>
         <v>0.846857142857143</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="25" t="n">
         <f aca="false">B16/((C16-D16)*$B$9+D16*$B$8)</f>
         <v>0.767080745341615</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="25" t="n">
         <f aca="false">B16/((C16-D16)*$C$9+D16*$B$8)</f>
         <v>0.872791519434629</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">204*$B$6+12*$B$8</f>
@@ -3915,12 +4580,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">155*$B$6+11*$B$8</f>
@@ -3929,7 +4594,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">155*$B$7+11*$B$8</f>
@@ -3938,7 +4603,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>3270</v>
@@ -3946,18 +4611,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B24" s="23" t="n">
+        <v>416</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <f aca="false">B23/B21</f>
         <v>0.942815953868333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B25" s="23" t="n">
+        <v>414</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <f aca="false">B23/B22</f>
         <v>0.820577164366374</v>
       </c>
@@ -3973,7 +4638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3989,36 +4654,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>165</v>
@@ -4026,14 +4691,14 @@
       <c r="C6" s="8" t="n">
         <v>169</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="19" t="n">
         <f aca="false">C6/B6-1</f>
         <v>0.0242424242424242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>429</v>
@@ -4041,14 +4706,14 @@
       <c r="C7" s="8" t="n">
         <v>406</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="19" t="n">
         <f aca="false">C7/B7-1</f>
         <v>-0.0536130536130536</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>263</v>
@@ -4056,14 +4721,14 @@
       <c r="C8" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <f aca="false">C8/B8-1</f>
         <v>-0.0114068441064639</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>430</v>
@@ -4071,14 +4736,14 @@
       <c r="C9" s="8" t="n">
         <v>337</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="19" t="n">
         <f aca="false">C9/B9-1</f>
         <v>-0.216279069767442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>284</v>
@@ -4086,14 +4751,14 @@
       <c r="C10" s="8" t="n">
         <v>298</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="19" t="n">
         <f aca="false">C10/B10-1</f>
         <v>0.0492957746478873</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>290</v>
@@ -4101,14 +4766,14 @@
       <c r="C11" s="8" t="n">
         <v>313</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="19" t="n">
         <f aca="false">C11/B11-1</f>
         <v>0.0793103448275863</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>185</v>
@@ -4116,14 +4781,14 @@
       <c r="C12" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="19" t="n">
         <f aca="false">C12/B12-1</f>
         <v>-0.0486486486486486</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>280</v>
@@ -4131,14 +4796,14 @@
       <c r="C13" s="8" t="n">
         <v>279</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="19" t="n">
         <f aca="false">C13/B13-1</f>
         <v>-0.00357142857142856</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>386</v>
@@ -4146,14 +4811,14 @@
       <c r="C14" s="8" t="n">
         <v>397</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">C14/B14-1</f>
         <v>0.028497409326425</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>353</v>
@@ -4161,14 +4826,14 @@
       <c r="C15" s="8" t="n">
         <v>391</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="19" t="n">
         <f aca="false">C15/B15-1</f>
         <v>0.107648725212464</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>332</v>
@@ -4176,14 +4841,14 @@
       <c r="C16" s="8" t="n">
         <v>336</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="19" t="n">
         <f aca="false">C16/B16-1</f>
         <v>0.0120481927710843</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B17" s="7" t="n">
         <f aca="false">SUM(B6:B16)</f>
@@ -4193,14 +4858,14 @@
         <f aca="false">SUM(C6:C16)</f>
         <v>3362</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="19" t="n">
         <f aca="false">C17/B17-1</f>
         <v>-0.0103032087135708</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">SUMPRODUCT(ABS(D6:D16))/COUNT(D6:D16)</f>
@@ -4209,7 +4874,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">STDEV(D6:D16)</f>
@@ -4218,26 +4883,26 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>181</v>
@@ -4245,14 +4910,14 @@
       <c r="C23" s="8" t="n">
         <v>166</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="19" t="n">
         <f aca="false">C23/B23-1</f>
         <v>-0.0828729281767956</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>378</v>
@@ -4260,14 +4925,14 @@
       <c r="C24" s="8" t="n">
         <v>382</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="19" t="n">
         <f aca="false">C24/B24-1</f>
         <v>0.0105820105820107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>286</v>
@@ -4275,14 +4940,14 @@
       <c r="C25" s="8" t="n">
         <v>271</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="19" t="n">
         <f aca="false">C25/B25-1</f>
         <v>-0.0524475524475524</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>335</v>
@@ -4290,14 +4955,14 @@
       <c r="C26" s="8" t="n">
         <v>271</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="19" t="n">
         <f aca="false">C26/B26-1</f>
         <v>-0.191044776119403</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>300</v>
@@ -4305,14 +4970,14 @@
       <c r="C27" s="8" t="n">
         <v>303</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="19" t="n">
         <f aca="false">C27/B27-1</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>326</v>
@@ -4320,14 +4985,14 @@
       <c r="C28" s="8" t="n">
         <v>306</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="19" t="n">
         <f aca="false">C28/B28-1</f>
         <v>-0.0613496932515337</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>175</v>
@@ -4335,14 +5000,14 @@
       <c r="C29" s="8" t="n">
         <v>160</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="19" t="n">
         <f aca="false">C29/B29-1</f>
         <v>-0.0857142857142857</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>273</v>
@@ -4350,14 +5015,14 @@
       <c r="C30" s="8" t="n">
         <v>275</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="19" t="n">
         <f aca="false">C30/B30-1</f>
         <v>0.0073260073260073</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>392</v>
@@ -4365,14 +5030,14 @@
       <c r="C31" s="8" t="n">
         <v>382</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="19" t="n">
         <f aca="false">C31/B31-1</f>
         <v>-0.0255102040816326</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>399</v>
@@ -4380,14 +5045,14 @@
       <c r="C32" s="8" t="n">
         <v>375</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="19" t="n">
         <f aca="false">C32/B32-1</f>
         <v>-0.0601503759398496</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>317</v>
@@ -4395,14 +5060,14 @@
       <c r="C33" s="8" t="n">
         <v>362</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="19" t="n">
         <f aca="false">C33/B33-1</f>
         <v>0.141955835962145</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">SUM(B23:B33)</f>
@@ -4412,14 +5077,14 @@
         <f aca="false">SUM(C23:C33)</f>
         <v>3253</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="19" t="n">
         <f aca="false">C34/B34-1</f>
         <v>-0.0324211778703153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="D35" s="10" t="n">
         <f aca="false">SUMPRODUCT(ABS(D23:D33))/COUNT(D23:D33)</f>
@@ -4428,7 +5093,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="D36" s="10" t="n">
         <f aca="false">STDEV(D23:D33)</f>
@@ -4451,7 +5116,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -4463,433 +5128,473 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4916,43 +5621,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>570</v>
@@ -4979,7 +5684,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>581</v>
@@ -5006,7 +5711,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>566</v>
@@ -5033,7 +5738,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>593</v>
@@ -5060,7 +5765,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>586</v>
@@ -5087,7 +5792,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>623</v>
@@ -5114,7 +5819,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>558</v>
@@ -5141,7 +5846,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>582</v>
@@ -5168,7 +5873,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>626</v>
@@ -5195,7 +5900,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>637</v>
@@ -5222,7 +5927,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>684</v>
@@ -5249,7 +5954,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>525</v>
@@ -5276,7 +5981,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>534</v>
@@ -5303,7 +6008,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>516</v>
@@ -5330,7 +6035,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>487</v>
@@ -5357,7 +6062,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>479</v>
@@ -5384,7 +6089,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>473</v>
@@ -5411,7 +6116,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>456</v>
@@ -5462,73 +6167,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>595</v>
@@ -5588,7 +6293,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>617</v>
@@ -5648,7 +6353,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>609</v>
@@ -5708,7 +6413,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>637</v>
@@ -5768,7 +6473,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>621</v>
@@ -5828,7 +6533,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>664</v>
@@ -5888,7 +6593,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>628</v>
@@ -5948,7 +6653,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>635</v>
@@ -6008,7 +6713,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>685</v>
@@ -6068,7 +6773,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>701</v>
@@ -6128,7 +6833,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>744</v>
@@ -6188,7 +6893,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>569</v>
@@ -6248,7 +6953,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>598</v>
@@ -6308,7 +7013,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>561</v>
@@ -6368,7 +7073,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>540</v>
@@ -6428,7 +7133,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>540</v>
@@ -6488,7 +7193,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>514</v>
@@ -6548,7 +7253,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>513</v>
@@ -6631,67 +7336,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>396</v>
@@ -6745,7 +7450,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>357</v>
@@ -6799,7 +7504,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>354</v>
@@ -6853,7 +7558,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>358</v>
@@ -6907,7 +7612,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>348</v>
@@ -6961,7 +7666,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>361</v>
@@ -7015,7 +7720,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>346</v>
@@ -7069,7 +7774,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>345</v>
@@ -7123,7 +7828,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>352</v>
@@ -7177,7 +7882,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>354</v>
@@ -7231,7 +7936,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>340</v>
@@ -7285,7 +7990,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>317</v>
@@ -7339,7 +8044,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>267</v>
@@ -7393,7 +8098,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>273</v>
@@ -7447,7 +8152,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>271</v>
@@ -7501,7 +8206,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>274</v>
@@ -7555,7 +8260,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>278</v>
@@ -7609,7 +8314,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>275</v>
@@ -7663,7 +8368,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B24" s="10" t="n">
         <f aca="false">B5/$O$5</f>
@@ -7724,7 +8429,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B25" s="10" t="n">
         <f aca="false">B22/$O$22</f>
@@ -7810,31 +8515,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>10</v>
@@ -7848,7 +8553,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>10</v>
@@ -7862,7 +8567,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>10</v>
@@ -7876,7 +8581,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>10</v>
@@ -7890,7 +8595,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>10</v>
@@ -7904,7 +8609,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>10</v>
@@ -7918,7 +8623,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>10</v>
@@ -7932,7 +8637,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>10</v>
@@ -7946,7 +8651,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>10</v>
@@ -7960,7 +8665,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>10</v>
@@ -7974,7 +8679,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>10</v>
@@ -7988,7 +8693,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>10</v>
@@ -8002,7 +8707,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>10</v>
@@ -8016,7 +8721,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>10</v>
@@ -8030,7 +8735,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>10</v>
@@ -8044,7 +8749,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>10</v>
@@ -8058,7 +8763,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>10</v>
@@ -8072,7 +8777,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>1</v>
@@ -8117,61 +8822,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>8.40000000008979</v>
@@ -8198,16 +8903,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>-13.071428572876</v>
@@ -8234,16 +8939,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>39.2727272731284</v>
@@ -8270,16 +8975,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>-67.9642857218498</v>
@@ -8306,16 +9011,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>-20.5593395248967</v>
@@ -8342,16 +9047,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>-5.7142857140002</v>
@@ -8378,16 +9083,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>-7.17142857107626</v>
@@ -8414,16 +9119,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>2.97142857132795</v>
@@ -8450,16 +9155,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>-6.94530443743452</v>
@@ -8486,16 +9191,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>-7.51190476153053</v>
@@ -8522,16 +9227,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>2.39525283793284</v>
@@ -8558,16 +9263,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>-8.22619047578042</v>
@@ -8594,16 +9299,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>0.463364293077175</v>
@@ -8630,16 +9335,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>-13.2142857136382</v>
@@ -8666,16 +9371,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>-8.14241486052869</v>
@@ -8702,16 +9407,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>-27.571428570078</v>
@@ -8738,16 +9443,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>-5.29824561393573</v>
@@ -8774,16 +9479,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>-17.9999999991117</v>
@@ -8810,16 +9515,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>-4.00619195038931</v>
@@ -8846,16 +9551,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>-12.1309523803538</v>
@@ -8882,16 +9587,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>-3.69040247671094</v>
@@ -8918,16 +9623,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>-5.23809523782861</v>
@@ -8954,16 +9659,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>-1.82662538696245</v>
@@ -8990,16 +9695,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>-6.90476190441343</v>
@@ -9026,16 +9731,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>5.88235294106692</v>
@@ -9062,16 +9767,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>5.55952380926769</v>
@@ -9098,16 +9803,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>-0.164086687303193</v>
@@ -9134,16 +9839,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>5.3809523807016</v>
@@ -9170,16 +9875,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>0.77296181629118</v>
@@ -9206,16 +9911,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>-3.38095238078222</v>
@@ -9242,16 +9947,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>-4.08668730642451</v>
@@ -9278,16 +9983,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>-28.9523809509492</v>
@@ -9314,16 +10019,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>-16.4726522184722</v>
@@ -9350,16 +10055,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>194</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>-62.2857142825985</v>
@@ -9386,16 +10091,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>-20.5593395248967</v>
@@ -9422,16 +10127,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>-91.2380952335477</v>
@@ -9458,16 +10163,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E41" s="16" t="n">
         <v>0.000150802282228644</v>
@@ -9494,16 +10199,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>26.7553921570288</v>
@@ -9530,16 +10235,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>105.276363637452</v>
@@ -9566,16 +10271,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>-59.9428571488777</v>
@@ -9602,16 +10307,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>-15.1514285682838</v>
@@ -9638,16 +10343,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>-23.2071428600748</v>
@@ -9695,34 +10400,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>4</v>
@@ -9737,7 +10442,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>4</v>
@@ -9749,12 +10454,12 @@
         <v>162.100656424827</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>4</v>
@@ -9766,12 +10471,12 @@
         <v>166.55539241034</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>4</v>
@@ -9783,12 +10488,12 @@
         <v>169.517722163865</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>4</v>
@@ -9800,12 +10505,12 @@
         <v>171.002613630221</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>3</v>
@@ -9820,7 +10525,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>2</v>
@@ -9858,42 +10563,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">Data_K5!C6/Data_K5!B5</f>
@@ -9918,7 +10623,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">Data_K5!C7/Data_K5!B6</f>
@@ -9943,7 +10648,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">Data_K5!C8/Data_K5!B7</f>
@@ -9968,7 +10673,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">Data_K5!C9/Data_K5!B8</f>
@@ -9993,7 +10698,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">Data_K5!C10/Data_K5!B9</f>
@@ -10018,7 +10723,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">Data_K5!C11/Data_K5!B10</f>
@@ -10043,7 +10748,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">Data_K5!C12/Data_K5!B11</f>
@@ -10068,7 +10773,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">Data_K5!C13/Data_K5!B12</f>
@@ -10093,7 +10798,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">Data_K5!C14/Data_K5!B13</f>
@@ -10118,7 +10823,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">Data_K5!C15/Data_K5!B14</f>
@@ -10143,7 +10848,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">Data_K5!C16/Data_K5!B15</f>
@@ -10168,7 +10873,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">Data_K5!C17/Data_K5!B16</f>
@@ -10193,7 +10898,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">Data_K5!C18/Data_K5!B17</f>
@@ -10218,7 +10923,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">Data_K5!C19/Data_K5!B18</f>
@@ -10243,7 +10948,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">Data_K5!C20/Data_K5!B19</f>
@@ -10268,7 +10973,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">Data_K5!C21/Data_K5!B20</f>
@@ -10293,7 +10998,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B22" s="16" t="n">
         <f aca="false">Data_K5!C22/Data_K5!B21</f>
@@ -10318,7 +11023,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B24" s="16" t="n">
         <f aca="false">AVERAGE(B6:B15)</f>
@@ -10343,7 +11048,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">STDEV(B6:B15)</f>
@@ -10368,7 +11073,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">AVERAGE(B18:B22)</f>
@@ -10393,7 +11098,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B27" s="16" t="n">
         <f aca="false">STDEV(B18:B22)</f>
@@ -10418,7 +11123,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B28" s="15" t="n">
         <f aca="false">TTEST(B6:B15,B18:B22,2,3)</f>
@@ -10443,53 +11148,53 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B33" s="16" t="n">
         <f aca="false">Data_AllPrograms!C6/Data_AllPrograms!B5</f>
@@ -10542,7 +11247,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B34" s="16" t="n">
         <f aca="false">Data_AllPrograms!C7/Data_AllPrograms!B6</f>
@@ -10595,7 +11300,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B35" s="16" t="n">
         <f aca="false">Data_AllPrograms!C8/Data_AllPrograms!B7</f>
@@ -10648,7 +11353,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B36" s="16" t="n">
         <f aca="false">Data_AllPrograms!C9/Data_AllPrograms!B8</f>
@@ -10701,7 +11406,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B37" s="16" t="n">
         <f aca="false">Data_AllPrograms!C10/Data_AllPrograms!B9</f>
@@ -10754,7 +11459,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">Data_AllPrograms!C11/Data_AllPrograms!B10</f>
@@ -10807,7 +11512,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">Data_AllPrograms!C12/Data_AllPrograms!B11</f>
@@ -10860,7 +11565,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B40" s="16" t="n">
         <f aca="false">Data_AllPrograms!C13/Data_AllPrograms!B12</f>
@@ -10913,7 +11618,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B41" s="16" t="n">
         <f aca="false">Data_AllPrograms!C14/Data_AllPrograms!B13</f>
@@ -10966,7 +11671,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">Data_AllPrograms!C15/Data_AllPrograms!B14</f>
@@ -11019,7 +11724,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">Data_AllPrograms!C16/Data_AllPrograms!B15</f>
@@ -11072,7 +11777,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B44" s="16" t="n">
         <f aca="false">Data_AllPrograms!C17/Data_AllPrograms!B16</f>
@@ -11125,7 +11830,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B45" s="16" t="n">
         <f aca="false">Data_AllPrograms!C18/Data_AllPrograms!B17</f>
@@ -11178,7 +11883,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B46" s="16" t="n">
         <f aca="false">Data_AllPrograms!C19/Data_AllPrograms!B18</f>
@@ -11231,7 +11936,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B47" s="16" t="n">
         <f aca="false">Data_AllPrograms!C20/Data_AllPrograms!B19</f>
@@ -11284,7 +11989,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B48" s="16" t="n">
         <f aca="false">Data_AllPrograms!C21/Data_AllPrograms!B20</f>
@@ -11337,7 +12042,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">Data_AllPrograms!C22/Data_AllPrograms!B21</f>
@@ -11390,7 +12095,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B51" s="16" t="n">
         <f aca="false">AVERAGE(B33:B42)</f>
@@ -11443,7 +12148,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B52" s="16" t="n">
         <f aca="false">STDEV(B33:B42)</f>
@@ -11496,7 +12201,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B53" s="16" t="n">
         <f aca="false">AVERAGE(B45:B49)</f>
@@ -11549,7 +12254,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B54" s="16" t="n">
         <f aca="false">STDEV(B45:B49)</f>
@@ -11602,7 +12307,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B55" s="15" t="n">
         <f aca="false">TTEST(B33:B42,B45:B49,2,3)</f>
